--- a/Test Data/Registration Data.xlsx
+++ b/Test Data/Registration Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\169419\Katalon Studio\TrainingDemoProject\Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A4BB46-C8CE-4102-BACB-B6E0D4A4C8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45CC710-4053-43F4-894C-FC5D4B1E3467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2DD3991C-CB93-4A4F-BB96-B90B2545A477}"/>
   </bookViews>
@@ -83,22 +83,22 @@
     <t>Password</t>
   </si>
   <si>
-    <t>ParaBank64</t>
-  </si>
-  <si>
-    <t>User64</t>
-  </si>
-  <si>
-    <t>ParaBank64User64</t>
-  </si>
-  <si>
-    <t>ParaBank70</t>
-  </si>
-  <si>
-    <t>User70</t>
-  </si>
-  <si>
-    <t>ParaBank70User70</t>
+    <t>ParaBank91</t>
+  </si>
+  <si>
+    <t>User91</t>
+  </si>
+  <si>
+    <t>ParaBank91User91</t>
+  </si>
+  <si>
+    <t>ParaBank92</t>
+  </si>
+  <si>
+    <t>User92</t>
+  </si>
+  <si>
+    <t>ParaBank92User92</t>
   </si>
 </sst>
 </file>
@@ -537,10 +537,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -561,7 +561,7 @@
         <v>123456789</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>12</v>
@@ -572,10 +572,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -596,7 +596,7 @@
         <v>123456789</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>12</v>

--- a/Test Data/Registration Data.xlsx
+++ b/Test Data/Registration Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\169419\Katalon Studio\TrainingDemoProject\Test Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45CC710-4053-43F4-894C-FC5D4B1E3467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B75B975-16BF-417B-BA49-1EC4500FD882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2DD3991C-CB93-4A4F-BB96-B90B2545A477}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>FirstName</t>
   </si>
@@ -83,22 +83,19 @@
     <t>Password</t>
   </si>
   <si>
-    <t>ParaBank91</t>
-  </si>
-  <si>
-    <t>User91</t>
-  </si>
-  <si>
-    <t>ParaBank91User91</t>
-  </si>
-  <si>
-    <t>ParaBank92</t>
-  </si>
-  <si>
-    <t>User92</t>
-  </si>
-  <si>
-    <t>ParaBank92User92</t>
+    <t>ParaBank15User15</t>
+  </si>
+  <si>
+    <t>ParaBank16</t>
+  </si>
+  <si>
+    <t>User16</t>
+  </si>
+  <si>
+    <t>ParaBank16User16</t>
+  </si>
+  <si>
+    <t>ParaBank15</t>
   </si>
 </sst>
 </file>
@@ -489,7 +486,7 @@
   <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
+    <col min="1" max="1" width="23.21875" customWidth="1"/>
     <col min="2" max="2" width="16.77734375" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -537,10 +534,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -561,7 +558,7 @@
         <v>123456789</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>12</v>
@@ -572,10 +569,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -596,7 +593,7 @@
         <v>123456789</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>12</v>
